--- a/mrp-panel-demanda/mrp-panel-demanda/data/MB5B/MB5B_ejemplo.xlsx
+++ b/mrp-panel-demanda/mrp-panel-demanda/data/MB5B/MB5B_ejemplo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="19">
   <si>
     <t>Material</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>ACOPLE FLEXIBLE TIPO L095</t>
+  </si>
+  <si>
+    <t>REPUESTO CRITICO USO MUY RARO</t>
   </si>
   <si>
     <t>UN</t>
@@ -403,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I345"/>
+  <dimension ref="A1:I388"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -461,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -490,7 +493,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -519,7 +522,7 @@
         <v>55</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -548,7 +551,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -577,7 +580,7 @@
         <v>146</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -606,7 +609,7 @@
         <v>114</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -635,7 +638,7 @@
         <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -664,7 +667,7 @@
         <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -693,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -722,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -751,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -780,7 +783,7 @@
         <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -809,7 +812,7 @@
         <v>90</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -838,7 +841,7 @@
         <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -867,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -896,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -925,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -954,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -983,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1012,7 +1015,7 @@
         <v>45</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1041,7 +1044,7 @@
         <v>85</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1070,7 +1073,7 @@
         <v>124</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1099,7 +1102,7 @@
         <v>77</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1128,7 +1131,7 @@
         <v>38</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1157,7 +1160,7 @@
         <v>77</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1186,7 +1189,7 @@
         <v>114</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1215,7 +1218,7 @@
         <v>152</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1244,7 +1247,7 @@
         <v>110</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1273,7 +1276,7 @@
         <v>68</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1302,7 +1305,7 @@
         <v>25</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1331,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1360,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1389,7 +1392,7 @@
         <v>38</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1418,7 +1421,7 @@
         <v>75</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1447,7 +1450,7 @@
         <v>31</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1476,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1505,7 +1508,7 @@
         <v>47</v>
       </c>
       <c r="I38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1534,7 +1537,7 @@
         <v>12</v>
       </c>
       <c r="I39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1563,7 +1566,7 @@
         <v>47</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1592,7 +1595,7 @@
         <v>3</v>
       </c>
       <c r="I41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1621,7 +1624,7 @@
         <v>47</v>
       </c>
       <c r="I42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1650,7 +1653,7 @@
         <v>91</v>
       </c>
       <c r="I43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1679,7 +1682,7 @@
         <v>134</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1708,7 +1711,7 @@
         <v>81</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1737,7 +1740,7 @@
         <v>55</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1766,7 +1769,7 @@
         <v>109</v>
       </c>
       <c r="I47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1795,7 +1798,7 @@
         <v>97</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1824,7 +1827,7 @@
         <v>68</v>
       </c>
       <c r="I49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -1853,7 +1856,7 @@
         <v>97</v>
       </c>
       <c r="I50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -1882,7 +1885,7 @@
         <v>85</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -1911,7 +1914,7 @@
         <v>79</v>
       </c>
       <c r="I52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -1940,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -1969,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -1998,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2027,7 +2030,7 @@
         <v>57</v>
       </c>
       <c r="I56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2056,7 +2059,7 @@
         <v>47</v>
       </c>
       <c r="I57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2085,7 +2088,7 @@
         <v>34</v>
       </c>
       <c r="I58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2114,7 +2117,7 @@
         <v>31</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2143,7 +2146,7 @@
         <v>34</v>
       </c>
       <c r="I60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2172,7 +2175,7 @@
         <v>117</v>
       </c>
       <c r="I61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2201,7 +2204,7 @@
         <v>49</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2230,7 +2233,7 @@
         <v>117</v>
       </c>
       <c r="I63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2259,7 +2262,7 @@
         <v>132</v>
       </c>
       <c r="I64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2288,7 +2291,7 @@
         <v>165</v>
       </c>
       <c r="I65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2317,7 +2320,7 @@
         <v>162</v>
       </c>
       <c r="I66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2346,7 +2349,7 @@
         <v>165</v>
       </c>
       <c r="I67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2375,7 +2378,7 @@
         <v>151</v>
       </c>
       <c r="I68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2404,7 +2407,7 @@
         <v>174</v>
       </c>
       <c r="I69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2433,7 +2436,7 @@
         <v>188</v>
       </c>
       <c r="I70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2462,7 +2465,7 @@
         <v>228</v>
       </c>
       <c r="I71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2491,7 +2494,7 @@
         <v>259</v>
       </c>
       <c r="I72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2520,7 +2523,7 @@
         <v>290</v>
       </c>
       <c r="I73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2549,7 +2552,7 @@
         <v>334</v>
       </c>
       <c r="I74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2578,7 +2581,7 @@
         <v>327</v>
       </c>
       <c r="I75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2607,7 +2610,7 @@
         <v>375</v>
       </c>
       <c r="I76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2636,7 +2639,7 @@
         <v>403</v>
       </c>
       <c r="I77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2665,7 +2668,7 @@
         <v>381</v>
       </c>
       <c r="I78" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2694,7 +2697,7 @@
         <v>346</v>
       </c>
       <c r="I79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2723,7 +2726,7 @@
         <v>381</v>
       </c>
       <c r="I80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2752,7 +2755,7 @@
         <v>417</v>
       </c>
       <c r="I81" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -2781,7 +2784,7 @@
         <v>454</v>
       </c>
       <c r="I82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -2810,7 +2813,7 @@
         <v>437</v>
       </c>
       <c r="I83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -2839,7 +2842,7 @@
         <v>411</v>
       </c>
       <c r="I84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -2868,7 +2871,7 @@
         <v>437</v>
       </c>
       <c r="I85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -2897,7 +2900,7 @@
         <v>288</v>
       </c>
       <c r="I86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -2926,7 +2929,7 @@
         <v>437</v>
       </c>
       <c r="I87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -2955,7 +2958,7 @@
         <v>100</v>
       </c>
       <c r="I88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -2984,7 +2987,7 @@
         <v>155</v>
       </c>
       <c r="I89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3013,7 +3016,7 @@
         <v>155</v>
       </c>
       <c r="I90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3042,7 +3045,7 @@
         <v>125</v>
       </c>
       <c r="I91" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3071,7 +3074,7 @@
         <v>178</v>
       </c>
       <c r="I92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3100,7 +3103,7 @@
         <v>178</v>
       </c>
       <c r="I93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3129,7 +3132,7 @@
         <v>216</v>
       </c>
       <c r="I94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3158,7 +3161,7 @@
         <v>216</v>
       </c>
       <c r="I95" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3187,7 +3190,7 @@
         <v>216</v>
       </c>
       <c r="I96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="I97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3245,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="I98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3274,7 +3277,7 @@
         <v>338</v>
       </c>
       <c r="I99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3303,7 +3306,7 @@
         <v>338</v>
       </c>
       <c r="I100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3332,7 +3335,7 @@
         <v>397</v>
       </c>
       <c r="I101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3361,7 +3364,7 @@
         <v>397</v>
       </c>
       <c r="I102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3390,7 +3393,7 @@
         <v>373</v>
       </c>
       <c r="I103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3419,7 +3422,7 @@
         <v>422</v>
       </c>
       <c r="I104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3448,7 +3451,7 @@
         <v>422</v>
       </c>
       <c r="I105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3477,7 +3480,7 @@
         <v>456</v>
       </c>
       <c r="I106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3506,7 +3509,7 @@
         <v>490</v>
       </c>
       <c r="I107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3535,7 +3538,7 @@
         <v>490</v>
       </c>
       <c r="I108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3564,7 +3567,7 @@
         <v>502</v>
       </c>
       <c r="I109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3593,7 +3596,7 @@
         <v>502</v>
       </c>
       <c r="I110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3622,7 +3625,7 @@
         <v>576</v>
       </c>
       <c r="I111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3651,7 +3654,7 @@
         <v>576</v>
       </c>
       <c r="I112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -3680,7 +3683,7 @@
         <v>559</v>
       </c>
       <c r="I113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -3709,7 +3712,7 @@
         <v>521</v>
       </c>
       <c r="I114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3738,7 +3741,7 @@
         <v>559</v>
       </c>
       <c r="I115" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3767,7 +3770,7 @@
         <v>559</v>
       </c>
       <c r="I116" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3796,7 +3799,7 @@
         <v>619</v>
       </c>
       <c r="I117" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -3825,7 +3828,7 @@
         <v>619</v>
       </c>
       <c r="I118" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -3854,7 +3857,7 @@
         <v>619</v>
       </c>
       <c r="I119" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3883,7 +3886,7 @@
         <v>619</v>
       </c>
       <c r="I120" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3912,7 +3915,7 @@
         <v>619</v>
       </c>
       <c r="I121" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -3941,7 +3944,7 @@
         <v>687</v>
       </c>
       <c r="I122" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -3970,7 +3973,7 @@
         <v>713</v>
       </c>
       <c r="I123" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -3999,7 +4002,7 @@
         <v>713</v>
       </c>
       <c r="I124" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4028,7 +4031,7 @@
         <v>713</v>
       </c>
       <c r="I125" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -4057,7 +4060,7 @@
         <v>713</v>
       </c>
       <c r="I126" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -4086,7 +4089,7 @@
         <v>703</v>
       </c>
       <c r="I127" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -4115,7 +4118,7 @@
         <v>730</v>
       </c>
       <c r="I128" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4144,7 +4147,7 @@
         <v>730</v>
       </c>
       <c r="I129" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -4173,7 +4176,7 @@
         <v>730</v>
       </c>
       <c r="I130" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -4202,7 +4205,7 @@
         <v>54</v>
       </c>
       <c r="I131" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4231,7 +4234,7 @@
         <v>100</v>
       </c>
       <c r="I132" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4260,7 +4263,7 @@
         <v>138</v>
       </c>
       <c r="I133" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4289,7 +4292,7 @@
         <v>185</v>
       </c>
       <c r="I134" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4318,7 +4321,7 @@
         <v>227</v>
       </c>
       <c r="I135" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4347,7 +4350,7 @@
         <v>266</v>
       </c>
       <c r="I136" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4376,7 +4379,7 @@
         <v>308</v>
       </c>
       <c r="I137" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4405,7 +4408,7 @@
         <v>360</v>
       </c>
       <c r="I138" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4434,7 +4437,7 @@
         <v>320</v>
       </c>
       <c r="I139" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4463,7 +4466,7 @@
         <v>279</v>
       </c>
       <c r="I140" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4492,7 +4495,7 @@
         <v>320</v>
       </c>
       <c r="I141" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -4521,7 +4524,7 @@
         <v>285</v>
       </c>
       <c r="I142" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4550,7 +4553,7 @@
         <v>320</v>
       </c>
       <c r="I143" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -4579,7 +4582,7 @@
         <v>362</v>
       </c>
       <c r="I144" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -4608,7 +4611,7 @@
         <v>320</v>
       </c>
       <c r="I145" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -4637,7 +4640,7 @@
         <v>285</v>
       </c>
       <c r="I146" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -4666,7 +4669,7 @@
         <v>332</v>
       </c>
       <c r="I147" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -4695,7 +4698,7 @@
         <v>304</v>
       </c>
       <c r="I148" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -4724,7 +4727,7 @@
         <v>271</v>
       </c>
       <c r="I149" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -4753,7 +4756,7 @@
         <v>309</v>
       </c>
       <c r="I150" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -4782,7 +4785,7 @@
         <v>346</v>
       </c>
       <c r="I151" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -4811,7 +4814,7 @@
         <v>384</v>
       </c>
       <c r="I152" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -4840,7 +4843,7 @@
         <v>436</v>
       </c>
       <c r="I153" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -4869,7 +4872,7 @@
         <v>483</v>
       </c>
       <c r="I154" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -4898,7 +4901,7 @@
         <v>441</v>
       </c>
       <c r="I155" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -4927,7 +4930,7 @@
         <v>403</v>
       </c>
       <c r="I156" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -4956,7 +4959,7 @@
         <v>365</v>
       </c>
       <c r="I157" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -4985,7 +4988,7 @@
         <v>324</v>
       </c>
       <c r="I158" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -5014,7 +5017,7 @@
         <v>365</v>
       </c>
       <c r="I159" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -5043,7 +5046,7 @@
         <v>327</v>
       </c>
       <c r="I160" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -5072,7 +5075,7 @@
         <v>365</v>
       </c>
       <c r="I161" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -5101,7 +5104,7 @@
         <v>332</v>
       </c>
       <c r="I162" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -5130,7 +5133,7 @@
         <v>292</v>
       </c>
       <c r="I163" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -5159,7 +5162,7 @@
         <v>236</v>
       </c>
       <c r="I164" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -5188,7 +5191,7 @@
         <v>292</v>
       </c>
       <c r="I165" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -5217,7 +5220,7 @@
         <v>333</v>
       </c>
       <c r="I166" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -5246,7 +5249,7 @@
         <v>382</v>
       </c>
       <c r="I167" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -5275,7 +5278,7 @@
         <v>423</v>
       </c>
       <c r="I168" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -5304,7 +5307,7 @@
         <v>383</v>
       </c>
       <c r="I169" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -5333,7 +5336,7 @@
         <v>344</v>
       </c>
       <c r="I170" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -5362,7 +5365,7 @@
         <v>309</v>
       </c>
       <c r="I171" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -5391,7 +5394,7 @@
         <v>344</v>
       </c>
       <c r="I172" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -5420,7 +5423,7 @@
         <v>387</v>
       </c>
       <c r="I173" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -5449,7 +5452,7 @@
         <v>83</v>
       </c>
       <c r="I174" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -5478,7 +5481,7 @@
         <v>100</v>
       </c>
       <c r="I175" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -5507,7 +5510,7 @@
         <v>100</v>
       </c>
       <c r="I176" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -5536,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="I177" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -5565,7 +5568,7 @@
         <v>100</v>
       </c>
       <c r="I178" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -5594,7 +5597,7 @@
         <v>154</v>
       </c>
       <c r="I179" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -5623,7 +5626,7 @@
         <v>154</v>
       </c>
       <c r="I180" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -5652,7 +5655,7 @@
         <v>154</v>
       </c>
       <c r="I181" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -5681,7 +5684,7 @@
         <v>154</v>
       </c>
       <c r="I182" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -5710,7 +5713,7 @@
         <v>195</v>
       </c>
       <c r="I183" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -5739,7 +5742,7 @@
         <v>248</v>
       </c>
       <c r="I184" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -5768,7 +5771,7 @@
         <v>248</v>
       </c>
       <c r="I185" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -5797,7 +5800,7 @@
         <v>248</v>
       </c>
       <c r="I186" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -5826,7 +5829,7 @@
         <v>263</v>
       </c>
       <c r="I187" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -5855,7 +5858,7 @@
         <v>245</v>
       </c>
       <c r="I188" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -5884,7 +5887,7 @@
         <v>208</v>
       </c>
       <c r="I189" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -5913,7 +5916,7 @@
         <v>208</v>
       </c>
       <c r="I190" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -5942,7 +5945,7 @@
         <v>208</v>
       </c>
       <c r="I191" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -5971,7 +5974,7 @@
         <v>248</v>
       </c>
       <c r="I192" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -6000,7 +6003,7 @@
         <v>321</v>
       </c>
       <c r="I193" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -6029,7 +6032,7 @@
         <v>394</v>
       </c>
       <c r="I194" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -6058,7 +6061,7 @@
         <v>366</v>
       </c>
       <c r="I195" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -6087,7 +6090,7 @@
         <v>358</v>
       </c>
       <c r="I196" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -6116,7 +6119,7 @@
         <v>358</v>
       </c>
       <c r="I197" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -6145,7 +6148,7 @@
         <v>332</v>
       </c>
       <c r="I198" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -6174,7 +6177,7 @@
         <v>406</v>
       </c>
       <c r="I199" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -6203,7 +6206,7 @@
         <v>443</v>
       </c>
       <c r="I200" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -6232,7 +6235,7 @@
         <v>451</v>
       </c>
       <c r="I201" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -6261,7 +6264,7 @@
         <v>451</v>
       </c>
       <c r="I202" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -6290,7 +6293,7 @@
         <v>474</v>
       </c>
       <c r="I203" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -6319,7 +6322,7 @@
         <v>455</v>
       </c>
       <c r="I204" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -6348,7 +6351,7 @@
         <v>455</v>
       </c>
       <c r="I205" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -6377,7 +6380,7 @@
         <v>423</v>
       </c>
       <c r="I206" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -6406,7 +6409,7 @@
         <v>389</v>
       </c>
       <c r="I207" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -6435,7 +6438,7 @@
         <v>389</v>
       </c>
       <c r="I208" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -6464,7 +6467,7 @@
         <v>389</v>
       </c>
       <c r="I209" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -6493,7 +6496,7 @@
         <v>365</v>
       </c>
       <c r="I210" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -6522,7 +6525,7 @@
         <v>329</v>
       </c>
       <c r="I211" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -6551,7 +6554,7 @@
         <v>301</v>
       </c>
       <c r="I212" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -6580,7 +6583,7 @@
         <v>354</v>
       </c>
       <c r="I213" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -6609,7 +6612,7 @@
         <v>354</v>
       </c>
       <c r="I214" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -6638,7 +6641,7 @@
         <v>399</v>
       </c>
       <c r="I215" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -6667,7 +6670,7 @@
         <v>383</v>
       </c>
       <c r="I216" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -6696,7 +6699,7 @@
         <v>148</v>
       </c>
       <c r="I217" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -6725,7 +6728,7 @@
         <v>146</v>
       </c>
       <c r="I218" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -6754,7 +6757,7 @@
         <v>132</v>
       </c>
       <c r="I219" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -6783,7 +6786,7 @@
         <v>112</v>
       </c>
       <c r="I220" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -6812,7 +6815,7 @@
         <v>105</v>
       </c>
       <c r="I221" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -6841,7 +6844,7 @@
         <v>76</v>
       </c>
       <c r="I222" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -6870,7 +6873,7 @@
         <v>72</v>
       </c>
       <c r="I223" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -6899,7 +6902,7 @@
         <v>98</v>
       </c>
       <c r="I224" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -6928,7 +6931,7 @@
         <v>61</v>
       </c>
       <c r="I225" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -6957,7 +6960,7 @@
         <v>32</v>
       </c>
       <c r="I226" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -6986,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="I227" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -7015,7 +7018,7 @@
         <v>64</v>
       </c>
       <c r="I228" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -7044,7 +7047,7 @@
         <v>83</v>
       </c>
       <c r="I229" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -7073,7 +7076,7 @@
         <v>77</v>
       </c>
       <c r="I230" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -7102,7 +7105,7 @@
         <v>94</v>
       </c>
       <c r="I231" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -7131,7 +7134,7 @@
         <v>118</v>
       </c>
       <c r="I232" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -7160,7 +7163,7 @@
         <v>214</v>
       </c>
       <c r="I233" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -7189,7 +7192,7 @@
         <v>192</v>
       </c>
       <c r="I234" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -7218,7 +7221,7 @@
         <v>257</v>
       </c>
       <c r="I235" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -7247,7 +7250,7 @@
         <v>162</v>
       </c>
       <c r="I236" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -7276,7 +7279,7 @@
         <v>155</v>
       </c>
       <c r="I237" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -7305,7 +7308,7 @@
         <v>115</v>
       </c>
       <c r="I238" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -7334,7 +7337,7 @@
         <v>155</v>
       </c>
       <c r="I239" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -7363,7 +7366,7 @@
         <v>111</v>
       </c>
       <c r="I240" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -7392,7 +7395,7 @@
         <v>80</v>
       </c>
       <c r="I241" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -7421,7 +7424,7 @@
         <v>56</v>
       </c>
       <c r="I242" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -7450,7 +7453,7 @@
         <v>53</v>
       </c>
       <c r="I243" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -7479,7 +7482,7 @@
         <v>56</v>
       </c>
       <c r="I244" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -7508,7 +7511,7 @@
         <v>28</v>
       </c>
       <c r="I245" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -7537,7 +7540,7 @@
         <v>6</v>
       </c>
       <c r="I246" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -7566,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="I247" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -7595,7 +7598,7 @@
         <v>6</v>
       </c>
       <c r="I248" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -7624,7 +7627,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -7653,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="I250" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -7682,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="I251" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -7711,7 +7714,7 @@
         <v>45</v>
       </c>
       <c r="I252" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -7740,7 +7743,7 @@
         <v>40</v>
       </c>
       <c r="I253" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -7769,7 +7772,7 @@
         <v>94</v>
       </c>
       <c r="I254" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -7798,7 +7801,7 @@
         <v>103</v>
       </c>
       <c r="I255" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -7827,7 +7830,7 @@
         <v>102</v>
       </c>
       <c r="I256" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -7856,7 +7859,7 @@
         <v>48</v>
       </c>
       <c r="I257" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -7885,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="I258" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -7914,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -7943,7 +7946,7 @@
         <v>100</v>
       </c>
       <c r="I260" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -7972,7 +7975,7 @@
         <v>100</v>
       </c>
       <c r="I261" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -8001,7 +8004,7 @@
         <v>156</v>
       </c>
       <c r="I262" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -8030,7 +8033,7 @@
         <v>232</v>
       </c>
       <c r="I263" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -8059,7 +8062,7 @@
         <v>232</v>
       </c>
       <c r="I264" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -8088,7 +8091,7 @@
         <v>275</v>
       </c>
       <c r="I265" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -8117,7 +8120,7 @@
         <v>275</v>
       </c>
       <c r="I266" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -8146,7 +8149,7 @@
         <v>310</v>
       </c>
       <c r="I267" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -8175,7 +8178,7 @@
         <v>310</v>
       </c>
       <c r="I268" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -8204,7 +8207,7 @@
         <v>310</v>
       </c>
       <c r="I269" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -8233,7 +8236,7 @@
         <v>382</v>
       </c>
       <c r="I270" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -8262,7 +8265,7 @@
         <v>382</v>
       </c>
       <c r="I271" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="272" spans="1:9">
@@ -8291,7 +8294,7 @@
         <v>382</v>
       </c>
       <c r="I272" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -8320,7 +8323,7 @@
         <v>444</v>
       </c>
       <c r="I273" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="274" spans="1:9">
@@ -8349,7 +8352,7 @@
         <v>444</v>
       </c>
       <c r="I274" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -8378,7 +8381,7 @@
         <v>483</v>
       </c>
       <c r="I275" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -8407,7 +8410,7 @@
         <v>517</v>
       </c>
       <c r="I276" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -8436,7 +8439,7 @@
         <v>517</v>
       </c>
       <c r="I277" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -8465,7 +8468,7 @@
         <v>517</v>
       </c>
       <c r="I278" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279" spans="1:9">
@@ -8494,7 +8497,7 @@
         <v>517</v>
       </c>
       <c r="I279" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -8523,7 +8526,7 @@
         <v>517</v>
       </c>
       <c r="I280" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -8552,7 +8555,7 @@
         <v>517</v>
       </c>
       <c r="I281" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -8581,7 +8584,7 @@
         <v>517</v>
       </c>
       <c r="I282" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="283" spans="1:9">
@@ -8610,7 +8613,7 @@
         <v>517</v>
       </c>
       <c r="I283" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="284" spans="1:9">
@@ -8639,7 +8642,7 @@
         <v>517</v>
       </c>
       <c r="I284" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="285" spans="1:9">
@@ -8668,7 +8671,7 @@
         <v>558</v>
       </c>
       <c r="I285" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -8697,7 +8700,7 @@
         <v>558</v>
       </c>
       <c r="I286" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="287" spans="1:9">
@@ -8726,7 +8729,7 @@
         <v>558</v>
       </c>
       <c r="I287" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="288" spans="1:9">
@@ -8755,7 +8758,7 @@
         <v>558</v>
       </c>
       <c r="I288" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289" spans="1:9">
@@ -8784,7 +8787,7 @@
         <v>585</v>
       </c>
       <c r="I289" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -8813,7 +8816,7 @@
         <v>585</v>
       </c>
       <c r="I290" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291" spans="1:9">
@@ -8842,7 +8845,7 @@
         <v>614</v>
       </c>
       <c r="I291" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="292" spans="1:9">
@@ -8871,7 +8874,7 @@
         <v>649</v>
       </c>
       <c r="I292" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="293" spans="1:9">
@@ -8900,7 +8903,7 @@
         <v>678</v>
       </c>
       <c r="I293" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="294" spans="1:9">
@@ -8929,7 +8932,7 @@
         <v>753</v>
       </c>
       <c r="I294" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="295" spans="1:9">
@@ -8958,7 +8961,7 @@
         <v>753</v>
       </c>
       <c r="I295" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="296" spans="1:9">
@@ -8987,7 +8990,7 @@
         <v>753</v>
       </c>
       <c r="I296" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="297" spans="1:9">
@@ -9016,7 +9019,7 @@
         <v>753</v>
       </c>
       <c r="I297" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -9045,7 +9048,7 @@
         <v>753</v>
       </c>
       <c r="I298" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -9074,7 +9077,7 @@
         <v>823</v>
       </c>
       <c r="I299" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -9103,7 +9106,7 @@
         <v>823</v>
       </c>
       <c r="I300" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="301" spans="1:9">
@@ -9132,7 +9135,7 @@
         <v>823</v>
       </c>
       <c r="I301" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="302" spans="1:9">
@@ -9161,7 +9164,7 @@
         <v>823</v>
       </c>
       <c r="I302" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="303" spans="1:9">
@@ -9190,7 +9193,7 @@
         <v>169</v>
       </c>
       <c r="I303" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="304" spans="1:9">
@@ -9219,7 +9222,7 @@
         <v>169</v>
       </c>
       <c r="I304" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -9248,7 +9251,7 @@
         <v>157</v>
       </c>
       <c r="I305" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="306" spans="1:9">
@@ -9277,7 +9280,7 @@
         <v>157</v>
       </c>
       <c r="I306" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -9306,7 +9309,7 @@
         <v>182</v>
       </c>
       <c r="I307" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="308" spans="1:9">
@@ -9335,7 +9338,7 @@
         <v>213</v>
       </c>
       <c r="I308" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="309" spans="1:9">
@@ -9364,7 +9367,7 @@
         <v>213</v>
       </c>
       <c r="I309" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="310" spans="1:9">
@@ -9393,7 +9396,7 @@
         <v>178</v>
       </c>
       <c r="I310" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="311" spans="1:9">
@@ -9422,7 +9425,7 @@
         <v>213</v>
       </c>
       <c r="I311" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="312" spans="1:9">
@@ -9451,7 +9454,7 @@
         <v>206</v>
       </c>
       <c r="I312" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="313" spans="1:9">
@@ -9480,7 +9483,7 @@
         <v>246</v>
       </c>
       <c r="I313" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="314" spans="1:9">
@@ -9509,7 +9512,7 @@
         <v>282</v>
       </c>
       <c r="I314" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="315" spans="1:9">
@@ -9538,7 +9541,7 @@
         <v>318</v>
       </c>
       <c r="I315" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -9567,7 +9570,7 @@
         <v>291</v>
       </c>
       <c r="I316" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -9596,7 +9599,7 @@
         <v>351</v>
       </c>
       <c r="I317" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -9625,7 +9628,7 @@
         <v>351</v>
       </c>
       <c r="I318" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="319" spans="1:9">
@@ -9654,7 +9657,7 @@
         <v>351</v>
       </c>
       <c r="I319" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -9683,7 +9686,7 @@
         <v>351</v>
       </c>
       <c r="I320" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -9712,7 +9715,7 @@
         <v>351</v>
       </c>
       <c r="I321" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -9741,7 +9744,7 @@
         <v>389</v>
       </c>
       <c r="I322" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -9770,7 +9773,7 @@
         <v>422</v>
       </c>
       <c r="I323" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -9799,7 +9802,7 @@
         <v>422</v>
       </c>
       <c r="I324" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -9828,7 +9831,7 @@
         <v>468</v>
       </c>
       <c r="I325" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -9857,7 +9860,7 @@
         <v>518</v>
       </c>
       <c r="I326" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -9886,7 +9889,7 @@
         <v>518</v>
       </c>
       <c r="I327" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -9915,7 +9918,7 @@
         <v>518</v>
       </c>
       <c r="I328" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="329" spans="1:9">
@@ -9944,7 +9947,7 @@
         <v>518</v>
       </c>
       <c r="I329" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -9973,7 +9976,7 @@
         <v>518</v>
       </c>
       <c r="I330" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="331" spans="1:9">
@@ -10002,7 +10005,7 @@
         <v>518</v>
       </c>
       <c r="I331" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="332" spans="1:9">
@@ -10031,7 +10034,7 @@
         <v>518</v>
       </c>
       <c r="I332" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="333" spans="1:9">
@@ -10060,7 +10063,7 @@
         <v>572</v>
       </c>
       <c r="I333" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="334" spans="1:9">
@@ -10089,7 +10092,7 @@
         <v>572</v>
       </c>
       <c r="I334" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="335" spans="1:9">
@@ -10118,7 +10121,7 @@
         <v>572</v>
       </c>
       <c r="I335" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="336" spans="1:9">
@@ -10147,7 +10150,7 @@
         <v>624</v>
       </c>
       <c r="I336" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="337" spans="1:9">
@@ -10176,7 +10179,7 @@
         <v>668</v>
       </c>
       <c r="I337" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -10205,7 +10208,7 @@
         <v>668</v>
       </c>
       <c r="I338" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="339" spans="1:9">
@@ -10234,7 +10237,7 @@
         <v>668</v>
       </c>
       <c r="I339" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="340" spans="1:9">
@@ -10263,7 +10266,7 @@
         <v>668</v>
       </c>
       <c r="I340" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="341" spans="1:9">
@@ -10292,7 +10295,7 @@
         <v>668</v>
       </c>
       <c r="I341" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -10321,7 +10324,7 @@
         <v>668</v>
       </c>
       <c r="I342" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -10350,7 +10353,7 @@
         <v>630</v>
       </c>
       <c r="I343" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -10379,7 +10382,7 @@
         <v>630</v>
       </c>
       <c r="I344" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -10408,7 +10411,1254 @@
         <v>630</v>
       </c>
       <c r="I345" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9">
+      <c r="A346">
+        <v>100009</v>
+      </c>
+      <c r="B346" t="s">
         <v>17</v>
+      </c>
+      <c r="C346" s="1">
+        <v>44927</v>
+      </c>
+      <c r="D346" s="1">
+        <v>44957</v>
+      </c>
+      <c r="E346">
+        <v>100</v>
+      </c>
+      <c r="F346">
+        <v>31</v>
+      </c>
+      <c r="G346">
+        <v>0</v>
+      </c>
+      <c r="H346">
+        <v>131</v>
+      </c>
+      <c r="I346" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9">
+      <c r="A347">
+        <v>100009</v>
+      </c>
+      <c r="B347" t="s">
+        <v>17</v>
+      </c>
+      <c r="C347" s="1">
+        <v>44958</v>
+      </c>
+      <c r="D347" s="1">
+        <v>44985</v>
+      </c>
+      <c r="E347">
+        <v>131</v>
+      </c>
+      <c r="F347">
+        <v>0</v>
+      </c>
+      <c r="G347">
+        <v>0</v>
+      </c>
+      <c r="H347">
+        <v>131</v>
+      </c>
+      <c r="I347" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9">
+      <c r="A348">
+        <v>100009</v>
+      </c>
+      <c r="B348" t="s">
+        <v>17</v>
+      </c>
+      <c r="C348" s="1">
+        <v>44986</v>
+      </c>
+      <c r="D348" s="1">
+        <v>45016</v>
+      </c>
+      <c r="E348">
+        <v>131</v>
+      </c>
+      <c r="F348">
+        <v>0</v>
+      </c>
+      <c r="G348">
+        <v>0</v>
+      </c>
+      <c r="H348">
+        <v>131</v>
+      </c>
+      <c r="I348" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9">
+      <c r="A349">
+        <v>100009</v>
+      </c>
+      <c r="B349" t="s">
+        <v>17</v>
+      </c>
+      <c r="C349" s="1">
+        <v>45017</v>
+      </c>
+      <c r="D349" s="1">
+        <v>45046</v>
+      </c>
+      <c r="E349">
+        <v>131</v>
+      </c>
+      <c r="F349">
+        <v>0</v>
+      </c>
+      <c r="G349">
+        <v>0</v>
+      </c>
+      <c r="H349">
+        <v>131</v>
+      </c>
+      <c r="I349" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9">
+      <c r="A350">
+        <v>100009</v>
+      </c>
+      <c r="B350" t="s">
+        <v>17</v>
+      </c>
+      <c r="C350" s="1">
+        <v>45047</v>
+      </c>
+      <c r="D350" s="1">
+        <v>45077</v>
+      </c>
+      <c r="E350">
+        <v>131</v>
+      </c>
+      <c r="F350">
+        <v>0</v>
+      </c>
+      <c r="G350">
+        <v>12</v>
+      </c>
+      <c r="H350">
+        <v>119</v>
+      </c>
+      <c r="I350" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351">
+        <v>100009</v>
+      </c>
+      <c r="B351" t="s">
+        <v>17</v>
+      </c>
+      <c r="C351" s="1">
+        <v>45078</v>
+      </c>
+      <c r="D351" s="1">
+        <v>45107</v>
+      </c>
+      <c r="E351">
+        <v>119</v>
+      </c>
+      <c r="F351">
+        <v>76</v>
+      </c>
+      <c r="G351">
+        <v>0</v>
+      </c>
+      <c r="H351">
+        <v>195</v>
+      </c>
+      <c r="I351" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352">
+        <v>100009</v>
+      </c>
+      <c r="B352" t="s">
+        <v>17</v>
+      </c>
+      <c r="C352" s="1">
+        <v>45108</v>
+      </c>
+      <c r="D352" s="1">
+        <v>45138</v>
+      </c>
+      <c r="E352">
+        <v>195</v>
+      </c>
+      <c r="F352">
+        <v>0</v>
+      </c>
+      <c r="G352">
+        <v>0</v>
+      </c>
+      <c r="H352">
+        <v>195</v>
+      </c>
+      <c r="I352" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353">
+        <v>100009</v>
+      </c>
+      <c r="B353" t="s">
+        <v>17</v>
+      </c>
+      <c r="C353" s="1">
+        <v>45139</v>
+      </c>
+      <c r="D353" s="1">
+        <v>45169</v>
+      </c>
+      <c r="E353">
+        <v>195</v>
+      </c>
+      <c r="F353">
+        <v>28</v>
+      </c>
+      <c r="G353">
+        <v>0</v>
+      </c>
+      <c r="H353">
+        <v>223</v>
+      </c>
+      <c r="I353" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9">
+      <c r="A354">
+        <v>100009</v>
+      </c>
+      <c r="B354" t="s">
+        <v>17</v>
+      </c>
+      <c r="C354" s="1">
+        <v>45170</v>
+      </c>
+      <c r="D354" s="1">
+        <v>45199</v>
+      </c>
+      <c r="E354">
+        <v>223</v>
+      </c>
+      <c r="F354">
+        <v>0</v>
+      </c>
+      <c r="G354">
+        <v>0</v>
+      </c>
+      <c r="H354">
+        <v>223</v>
+      </c>
+      <c r="I354" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9">
+      <c r="A355">
+        <v>100009</v>
+      </c>
+      <c r="B355" t="s">
+        <v>17</v>
+      </c>
+      <c r="C355" s="1">
+        <v>45200</v>
+      </c>
+      <c r="D355" s="1">
+        <v>45230</v>
+      </c>
+      <c r="E355">
+        <v>223</v>
+      </c>
+      <c r="F355">
+        <v>0</v>
+      </c>
+      <c r="G355">
+        <v>0</v>
+      </c>
+      <c r="H355">
+        <v>223</v>
+      </c>
+      <c r="I355" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9">
+      <c r="A356">
+        <v>100009</v>
+      </c>
+      <c r="B356" t="s">
+        <v>17</v>
+      </c>
+      <c r="C356" s="1">
+        <v>45231</v>
+      </c>
+      <c r="D356" s="1">
+        <v>45260</v>
+      </c>
+      <c r="E356">
+        <v>223</v>
+      </c>
+      <c r="F356">
+        <v>62</v>
+      </c>
+      <c r="G356">
+        <v>0</v>
+      </c>
+      <c r="H356">
+        <v>285</v>
+      </c>
+      <c r="I356" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9">
+      <c r="A357">
+        <v>100009</v>
+      </c>
+      <c r="B357" t="s">
+        <v>17</v>
+      </c>
+      <c r="C357" s="1">
+        <v>45261</v>
+      </c>
+      <c r="D357" s="1">
+        <v>45291</v>
+      </c>
+      <c r="E357">
+        <v>285</v>
+      </c>
+      <c r="F357">
+        <v>69</v>
+      </c>
+      <c r="G357">
+        <v>0</v>
+      </c>
+      <c r="H357">
+        <v>354</v>
+      </c>
+      <c r="I357" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9">
+      <c r="A358">
+        <v>100009</v>
+      </c>
+      <c r="B358" t="s">
+        <v>17</v>
+      </c>
+      <c r="C358" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D358" s="1">
+        <v>45322</v>
+      </c>
+      <c r="E358">
+        <v>354</v>
+      </c>
+      <c r="F358">
+        <v>0</v>
+      </c>
+      <c r="G358">
+        <v>0</v>
+      </c>
+      <c r="H358">
+        <v>354</v>
+      </c>
+      <c r="I358" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9">
+      <c r="A359">
+        <v>100009</v>
+      </c>
+      <c r="B359" t="s">
+        <v>17</v>
+      </c>
+      <c r="C359" s="1">
+        <v>45323</v>
+      </c>
+      <c r="D359" s="1">
+        <v>45351</v>
+      </c>
+      <c r="E359">
+        <v>354</v>
+      </c>
+      <c r="F359">
+        <v>0</v>
+      </c>
+      <c r="G359">
+        <v>0</v>
+      </c>
+      <c r="H359">
+        <v>354</v>
+      </c>
+      <c r="I359" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9">
+      <c r="A360">
+        <v>100009</v>
+      </c>
+      <c r="B360" t="s">
+        <v>17</v>
+      </c>
+      <c r="C360" s="1">
+        <v>45352</v>
+      </c>
+      <c r="D360" s="1">
+        <v>45382</v>
+      </c>
+      <c r="E360">
+        <v>354</v>
+      </c>
+      <c r="F360">
+        <v>0</v>
+      </c>
+      <c r="G360">
+        <v>0</v>
+      </c>
+      <c r="H360">
+        <v>354</v>
+      </c>
+      <c r="I360" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9">
+      <c r="A361">
+        <v>100009</v>
+      </c>
+      <c r="B361" t="s">
+        <v>17</v>
+      </c>
+      <c r="C361" s="1">
+        <v>45383</v>
+      </c>
+      <c r="D361" s="1">
+        <v>45412</v>
+      </c>
+      <c r="E361">
+        <v>354</v>
+      </c>
+      <c r="F361">
+        <v>0</v>
+      </c>
+      <c r="G361">
+        <v>0</v>
+      </c>
+      <c r="H361">
+        <v>354</v>
+      </c>
+      <c r="I361" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9">
+      <c r="A362">
+        <v>100009</v>
+      </c>
+      <c r="B362" t="s">
+        <v>17</v>
+      </c>
+      <c r="C362" s="1">
+        <v>45413</v>
+      </c>
+      <c r="D362" s="1">
+        <v>45443</v>
+      </c>
+      <c r="E362">
+        <v>354</v>
+      </c>
+      <c r="F362">
+        <v>0</v>
+      </c>
+      <c r="G362">
+        <v>29</v>
+      </c>
+      <c r="H362">
+        <v>325</v>
+      </c>
+      <c r="I362" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9">
+      <c r="A363">
+        <v>100009</v>
+      </c>
+      <c r="B363" t="s">
+        <v>17</v>
+      </c>
+      <c r="C363" s="1">
+        <v>45444</v>
+      </c>
+      <c r="D363" s="1">
+        <v>45473</v>
+      </c>
+      <c r="E363">
+        <v>325</v>
+      </c>
+      <c r="F363">
+        <v>0</v>
+      </c>
+      <c r="G363">
+        <v>0</v>
+      </c>
+      <c r="H363">
+        <v>325</v>
+      </c>
+      <c r="I363" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364">
+        <v>100009</v>
+      </c>
+      <c r="B364" t="s">
+        <v>17</v>
+      </c>
+      <c r="C364" s="1">
+        <v>45474</v>
+      </c>
+      <c r="D364" s="1">
+        <v>45504</v>
+      </c>
+      <c r="E364">
+        <v>325</v>
+      </c>
+      <c r="F364">
+        <v>0</v>
+      </c>
+      <c r="G364">
+        <v>0</v>
+      </c>
+      <c r="H364">
+        <v>325</v>
+      </c>
+      <c r="I364" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365">
+        <v>100009</v>
+      </c>
+      <c r="B365" t="s">
+        <v>17</v>
+      </c>
+      <c r="C365" s="1">
+        <v>45505</v>
+      </c>
+      <c r="D365" s="1">
+        <v>45535</v>
+      </c>
+      <c r="E365">
+        <v>325</v>
+      </c>
+      <c r="F365">
+        <v>0</v>
+      </c>
+      <c r="G365">
+        <v>0</v>
+      </c>
+      <c r="H365">
+        <v>325</v>
+      </c>
+      <c r="I365" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366">
+        <v>100009</v>
+      </c>
+      <c r="B366" t="s">
+        <v>17</v>
+      </c>
+      <c r="C366" s="1">
+        <v>45536</v>
+      </c>
+      <c r="D366" s="1">
+        <v>45565</v>
+      </c>
+      <c r="E366">
+        <v>325</v>
+      </c>
+      <c r="F366">
+        <v>61</v>
+      </c>
+      <c r="G366">
+        <v>0</v>
+      </c>
+      <c r="H366">
+        <v>386</v>
+      </c>
+      <c r="I366" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367">
+        <v>100009</v>
+      </c>
+      <c r="B367" t="s">
+        <v>17</v>
+      </c>
+      <c r="C367" s="1">
+        <v>45566</v>
+      </c>
+      <c r="D367" s="1">
+        <v>45596</v>
+      </c>
+      <c r="E367">
+        <v>386</v>
+      </c>
+      <c r="F367">
+        <v>0</v>
+      </c>
+      <c r="G367">
+        <v>0</v>
+      </c>
+      <c r="H367">
+        <v>386</v>
+      </c>
+      <c r="I367" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9">
+      <c r="A368">
+        <v>100009</v>
+      </c>
+      <c r="B368" t="s">
+        <v>17</v>
+      </c>
+      <c r="C368" s="1">
+        <v>45597</v>
+      </c>
+      <c r="D368" s="1">
+        <v>45626</v>
+      </c>
+      <c r="E368">
+        <v>386</v>
+      </c>
+      <c r="F368">
+        <v>63</v>
+      </c>
+      <c r="G368">
+        <v>0</v>
+      </c>
+      <c r="H368">
+        <v>449</v>
+      </c>
+      <c r="I368" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9">
+      <c r="A369">
+        <v>100009</v>
+      </c>
+      <c r="B369" t="s">
+        <v>17</v>
+      </c>
+      <c r="C369" s="1">
+        <v>45627</v>
+      </c>
+      <c r="D369" s="1">
+        <v>45657</v>
+      </c>
+      <c r="E369">
+        <v>449</v>
+      </c>
+      <c r="F369">
+        <v>0</v>
+      </c>
+      <c r="G369">
+        <v>0</v>
+      </c>
+      <c r="H369">
+        <v>449</v>
+      </c>
+      <c r="I369" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9">
+      <c r="A370">
+        <v>100009</v>
+      </c>
+      <c r="B370" t="s">
+        <v>17</v>
+      </c>
+      <c r="C370" s="1">
+        <v>45658</v>
+      </c>
+      <c r="D370" s="1">
+        <v>45688</v>
+      </c>
+      <c r="E370">
+        <v>449</v>
+      </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
+      <c r="G370">
+        <v>0</v>
+      </c>
+      <c r="H370">
+        <v>449</v>
+      </c>
+      <c r="I370" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9">
+      <c r="A371">
+        <v>100009</v>
+      </c>
+      <c r="B371" t="s">
+        <v>17</v>
+      </c>
+      <c r="C371" s="1">
+        <v>45689</v>
+      </c>
+      <c r="D371" s="1">
+        <v>45716</v>
+      </c>
+      <c r="E371">
+        <v>449</v>
+      </c>
+      <c r="F371">
+        <v>42</v>
+      </c>
+      <c r="G371">
+        <v>0</v>
+      </c>
+      <c r="H371">
+        <v>491</v>
+      </c>
+      <c r="I371" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9">
+      <c r="A372">
+        <v>100009</v>
+      </c>
+      <c r="B372" t="s">
+        <v>17</v>
+      </c>
+      <c r="C372" s="1">
+        <v>45717</v>
+      </c>
+      <c r="D372" s="1">
+        <v>45747</v>
+      </c>
+      <c r="E372">
+        <v>491</v>
+      </c>
+      <c r="F372">
+        <v>60</v>
+      </c>
+      <c r="G372">
+        <v>0</v>
+      </c>
+      <c r="H372">
+        <v>551</v>
+      </c>
+      <c r="I372" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9">
+      <c r="A373">
+        <v>100009</v>
+      </c>
+      <c r="B373" t="s">
+        <v>17</v>
+      </c>
+      <c r="C373" s="1">
+        <v>45748</v>
+      </c>
+      <c r="D373" s="1">
+        <v>45777</v>
+      </c>
+      <c r="E373">
+        <v>551</v>
+      </c>
+      <c r="F373">
+        <v>0</v>
+      </c>
+      <c r="G373">
+        <v>0</v>
+      </c>
+      <c r="H373">
+        <v>551</v>
+      </c>
+      <c r="I373" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9">
+      <c r="A374">
+        <v>100009</v>
+      </c>
+      <c r="B374" t="s">
+        <v>17</v>
+      </c>
+      <c r="C374" s="1">
+        <v>45778</v>
+      </c>
+      <c r="D374" s="1">
+        <v>45808</v>
+      </c>
+      <c r="E374">
+        <v>551</v>
+      </c>
+      <c r="F374">
+        <v>0</v>
+      </c>
+      <c r="G374">
+        <v>0</v>
+      </c>
+      <c r="H374">
+        <v>551</v>
+      </c>
+      <c r="I374" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9">
+      <c r="A375">
+        <v>100009</v>
+      </c>
+      <c r="B375" t="s">
+        <v>17</v>
+      </c>
+      <c r="C375" s="1">
+        <v>45809</v>
+      </c>
+      <c r="D375" s="1">
+        <v>45838</v>
+      </c>
+      <c r="E375">
+        <v>551</v>
+      </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
+      <c r="G375">
+        <v>0</v>
+      </c>
+      <c r="H375">
+        <v>551</v>
+      </c>
+      <c r="I375" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9">
+      <c r="A376">
+        <v>100009</v>
+      </c>
+      <c r="B376" t="s">
+        <v>17</v>
+      </c>
+      <c r="C376" s="1">
+        <v>45839</v>
+      </c>
+      <c r="D376" s="1">
+        <v>45869</v>
+      </c>
+      <c r="E376">
+        <v>551</v>
+      </c>
+      <c r="F376">
+        <v>0</v>
+      </c>
+      <c r="G376">
+        <v>0</v>
+      </c>
+      <c r="H376">
+        <v>551</v>
+      </c>
+      <c r="I376" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9">
+      <c r="A377">
+        <v>100009</v>
+      </c>
+      <c r="B377" t="s">
+        <v>17</v>
+      </c>
+      <c r="C377" s="1">
+        <v>45870</v>
+      </c>
+      <c r="D377" s="1">
+        <v>45900</v>
+      </c>
+      <c r="E377">
+        <v>551</v>
+      </c>
+      <c r="F377">
+        <v>34</v>
+      </c>
+      <c r="G377">
+        <v>0</v>
+      </c>
+      <c r="H377">
+        <v>585</v>
+      </c>
+      <c r="I377" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9">
+      <c r="A378">
+        <v>100009</v>
+      </c>
+      <c r="B378" t="s">
+        <v>17</v>
+      </c>
+      <c r="C378" s="1">
+        <v>45901</v>
+      </c>
+      <c r="D378" s="1">
+        <v>45930</v>
+      </c>
+      <c r="E378">
+        <v>585</v>
+      </c>
+      <c r="F378">
+        <v>0</v>
+      </c>
+      <c r="G378">
+        <v>0</v>
+      </c>
+      <c r="H378">
+        <v>585</v>
+      </c>
+      <c r="I378" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9">
+      <c r="A379">
+        <v>100009</v>
+      </c>
+      <c r="B379" t="s">
+        <v>17</v>
+      </c>
+      <c r="C379" s="1">
+        <v>45931</v>
+      </c>
+      <c r="D379" s="1">
+        <v>45961</v>
+      </c>
+      <c r="E379">
+        <v>585</v>
+      </c>
+      <c r="F379">
+        <v>0</v>
+      </c>
+      <c r="G379">
+        <v>0</v>
+      </c>
+      <c r="H379">
+        <v>585</v>
+      </c>
+      <c r="I379" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9">
+      <c r="A380">
+        <v>100009</v>
+      </c>
+      <c r="B380" t="s">
+        <v>17</v>
+      </c>
+      <c r="C380" s="1">
+        <v>45962</v>
+      </c>
+      <c r="D380" s="1">
+        <v>45991</v>
+      </c>
+      <c r="E380">
+        <v>585</v>
+      </c>
+      <c r="F380">
+        <v>0</v>
+      </c>
+      <c r="G380">
+        <v>0</v>
+      </c>
+      <c r="H380">
+        <v>585</v>
+      </c>
+      <c r="I380" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9">
+      <c r="A381">
+        <v>100009</v>
+      </c>
+      <c r="B381" t="s">
+        <v>17</v>
+      </c>
+      <c r="C381" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D381" s="1">
+        <v>46022</v>
+      </c>
+      <c r="E381">
+        <v>585</v>
+      </c>
+      <c r="F381">
+        <v>64</v>
+      </c>
+      <c r="G381">
+        <v>0</v>
+      </c>
+      <c r="H381">
+        <v>649</v>
+      </c>
+      <c r="I381" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9">
+      <c r="A382">
+        <v>100009</v>
+      </c>
+      <c r="B382" t="s">
+        <v>17</v>
+      </c>
+      <c r="C382" s="1">
+        <v>46023</v>
+      </c>
+      <c r="D382" s="1">
+        <v>46053</v>
+      </c>
+      <c r="E382">
+        <v>649</v>
+      </c>
+      <c r="F382">
+        <v>0</v>
+      </c>
+      <c r="G382">
+        <v>0</v>
+      </c>
+      <c r="H382">
+        <v>649</v>
+      </c>
+      <c r="I382" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9">
+      <c r="A383">
+        <v>100009</v>
+      </c>
+      <c r="B383" t="s">
+        <v>17</v>
+      </c>
+      <c r="C383" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D383" s="1">
+        <v>46081</v>
+      </c>
+      <c r="E383">
+        <v>649</v>
+      </c>
+      <c r="F383">
+        <v>39</v>
+      </c>
+      <c r="G383">
+        <v>0</v>
+      </c>
+      <c r="H383">
+        <v>688</v>
+      </c>
+      <c r="I383" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9">
+      <c r="A384">
+        <v>100009</v>
+      </c>
+      <c r="B384" t="s">
+        <v>17</v>
+      </c>
+      <c r="C384" s="1">
+        <v>46082</v>
+      </c>
+      <c r="D384" s="1">
+        <v>46112</v>
+      </c>
+      <c r="E384">
+        <v>688</v>
+      </c>
+      <c r="F384">
+        <v>0</v>
+      </c>
+      <c r="G384">
+        <v>0</v>
+      </c>
+      <c r="H384">
+        <v>688</v>
+      </c>
+      <c r="I384" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="A385">
+        <v>100009</v>
+      </c>
+      <c r="B385" t="s">
+        <v>17</v>
+      </c>
+      <c r="C385" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D385" s="1">
+        <v>46142</v>
+      </c>
+      <c r="E385">
+        <v>688</v>
+      </c>
+      <c r="F385">
+        <v>29</v>
+      </c>
+      <c r="G385">
+        <v>0</v>
+      </c>
+      <c r="H385">
+        <v>717</v>
+      </c>
+      <c r="I385" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="A386">
+        <v>100009</v>
+      </c>
+      <c r="B386" t="s">
+        <v>17</v>
+      </c>
+      <c r="C386" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D386" s="1">
+        <v>46173</v>
+      </c>
+      <c r="E386">
+        <v>717</v>
+      </c>
+      <c r="F386">
+        <v>33</v>
+      </c>
+      <c r="G386">
+        <v>0</v>
+      </c>
+      <c r="H386">
+        <v>750</v>
+      </c>
+      <c r="I386" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387">
+        <v>100009</v>
+      </c>
+      <c r="B387" t="s">
+        <v>17</v>
+      </c>
+      <c r="C387" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D387" s="1">
+        <v>46203</v>
+      </c>
+      <c r="E387">
+        <v>750</v>
+      </c>
+      <c r="F387">
+        <v>0</v>
+      </c>
+      <c r="G387">
+        <v>0</v>
+      </c>
+      <c r="H387">
+        <v>750</v>
+      </c>
+      <c r="I387" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388">
+        <v>100009</v>
+      </c>
+      <c r="B388" t="s">
+        <v>17</v>
+      </c>
+      <c r="C388" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D388" s="1">
+        <v>46234</v>
+      </c>
+      <c r="E388">
+        <v>750</v>
+      </c>
+      <c r="F388">
+        <v>0</v>
+      </c>
+      <c r="G388">
+        <v>0</v>
+      </c>
+      <c r="H388">
+        <v>750</v>
+      </c>
+      <c r="I388" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
